--- a/output/第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx
+++ b/output/第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx
@@ -948,7 +948,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>令和7年度か令和8年度かを選ぶ項目がある。当方の検証では単価は改定の有無に関係なく年率1.75％で伸びており、令和7年度で固定することは月額で＋185〜＋374円に当たる。施設・居住系と在宅で別に選べるため、そろえるかどうかを含めご判断いただきたい（確認事項No.137）</t>
+          <t>令和7年度か令和8年度かを選ぶ項目がある。当方の検証では単価は改定の有無に関係なく年率1.75％で伸びており、令和7年度で固定することは単価の趨勢を落としており、月額への効きはサービス見込量の算定及び計画素案 第6章第6節2による。施設・居住系と在宅で別に選べるため、そろえるかどうかを含めご判断いただきたい（確認事項No.137）</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>「推計方法の設定」には、1人1月あたり給付費の実績値を令和7年度とするか令和8年度とするかを選ぶ項目があり、施設・居住系と在宅で別に選べる。①当方は令和7年度（12か月の完結年度）を選ぶ案としたい。②ただし当方の検証では、単価は介護報酬改定の有無に関係なく年率1.75％で伸びており（構成を固定した連鎖ラスパイレス指数で7年＋12.93％）、令和7年度で固定することは月額で＋185〜＋374円に当たる。③令和9年度は介護報酬改定の年である（3年周期。第10期の初年度）。改定率1％あたり月額＋61円である。④施設・居住系と在宅で年度をそろえるかどうかも併せてご判断いただきたい。</t>
+          <t>「推計方法の設定」には、1人1月あたり給付費の実績値を令和7年度とするか令和8年度とするかを選ぶ項目があり、施設・居住系と在宅で別に選べる。①当方は令和7年度（12か月の完結年度）を選ぶ案としたい。②ただし当方の検証では、単価は介護報酬改定の有無に関係なく年率1.75％で伸びており（構成を固定した連鎖ラスパイレス指数で7年＋12.93％）、令和7年度で固定することは月額で単価の趨勢を落としており、月額への効きはサービス見込量の算定及び計画素案 第6章第6節2による。③令和9年度は介護報酬改定の年である（3年周期。第10期の初年度）。改定率1％あたり月額＋61円である。④施設・居住系と在宅で年度をそろえるかどうかも併せてご判断いただきたい。</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">

--- a/output/第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx
+++ b/output/第10期計画_見える化_令和8年度実績見込み値の入力案.xlsx
@@ -6163,7 +6163,7 @@
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>将来推計 第2段階
-サービス見込量 第1次概算</t>
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
